--- a/output/topology_excel/12203.xlsx
+++ b/output/topology_excel/12203.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,680 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RoomA</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>RoomB</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>ConnectionType</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Length</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>220</v>
+      </c>
+      <c r="F2" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>194</v>
+      </c>
+      <c r="F3" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>165</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>436</v>
+      </c>
+      <c r="F5" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>268</v>
+      </c>
+      <c r="F6" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>90</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" t="n">
+        <v>10</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>51</v>
+      </c>
+      <c r="F8" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>235</v>
+      </c>
+      <c r="F9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>469</v>
+      </c>
+      <c r="F10" t="n">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>196</v>
+      </c>
+      <c r="F11" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>193</v>
+      </c>
+      <c r="F12" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>417</v>
+      </c>
+      <c r="F13" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>165</v>
+      </c>
+      <c r="F14" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>180</v>
+      </c>
+      <c r="F15" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>141</v>
+      </c>
+      <c r="F16" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B17" t="n">
+        <v>11</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>125</v>
+      </c>
+      <c r="F17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7</v>
+      </c>
+      <c r="B18" t="n">
+        <v>10</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>163</v>
+      </c>
+      <c r="F18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B19" t="n">
+        <v>9</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>259</v>
+      </c>
+      <c r="F19" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B20" t="n">
+        <v>9</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>216</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="n">
+        <v>7</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>91</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" t="n">
+        <v>9</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>142</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B23" t="n">
+        <v>7</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>129</v>
+      </c>
+      <c r="F23" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>69</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>72</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" t="n">
+        <v>10</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>200</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B27" t="n">
+        <v>7</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>73</v>
+      </c>
+      <c r="F27" t="n">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>72</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4</v>
+      </c>
+      <c r="B29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>69</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>6</v>
+      </c>
+      <c r="B30" t="n">
+        <v>11</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>75</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/topology_excel/12203.xlsx
+++ b/output/topology_excel/12203.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -479,8 +489,10 @@
         <v>220</v>
       </c>
       <c r="F2" t="n">
-        <v>73</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -501,8 +513,10 @@
         <v>194</v>
       </c>
       <c r="F3" t="n">
-        <v>87</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>18</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -545,8 +561,10 @@
         <v>436</v>
       </c>
       <c r="F5" t="n">
-        <v>76</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -567,8 +585,10 @@
         <v>268</v>
       </c>
       <c r="F6" t="n">
-        <v>90</v>
-      </c>
+        <v>21</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>1</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -611,8 +633,10 @@
         <v>51</v>
       </c>
       <c r="F8" t="n">
-        <v>38</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>17</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -649,13 +675,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>469</v>
+        <v>237</v>
       </c>
       <c r="F10" t="n">
-        <v>401</v>
+        <v>17</v>
+      </c>
+      <c r="G10" t="n">
+        <v>361</v>
+      </c>
+      <c r="H10" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -679,6 +711,8 @@
       <c r="F11" t="n">
         <v>17</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -699,8 +733,10 @@
         <v>193</v>
       </c>
       <c r="F12" t="n">
-        <v>39</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -715,13 +751,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>417</v>
+        <v>22</v>
       </c>
       <c r="F13" t="n">
-        <v>38</v>
+        <v>18</v>
+      </c>
+      <c r="G13" t="n">
+        <v>326</v>
+      </c>
+      <c r="H13" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="14">
@@ -737,12 +779,18 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>165</v>
+        <v>21</v>
       </c>
       <c r="F14" t="n">
+        <v>17</v>
+      </c>
+      <c r="G14" t="n">
+        <v>72</v>
+      </c>
+      <c r="H14" t="n">
         <v>17</v>
       </c>
     </row>
@@ -759,13 +807,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>180</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
         <v>18</v>
+      </c>
+      <c r="G15" t="n">
+        <v>39</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -789,6 +843,8 @@
       <c r="F16" t="n">
         <v>18</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +867,8 @@
       <c r="F17" t="n">
         <v>16</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -825,14 +883,20 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>163</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
         <v>17</v>
       </c>
+      <c r="G18" t="n">
+        <v>21</v>
+      </c>
+      <c r="H18" t="n">
+        <v>17</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -847,14 +911,20 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>259</v>
+        <v>60</v>
       </c>
       <c r="F19" t="n">
         <v>16</v>
       </c>
+      <c r="G19" t="n">
+        <v>57</v>
+      </c>
+      <c r="H19" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +947,8 @@
       <c r="F20" t="n">
         <v>1</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +971,8 @@
       <c r="F21" t="n">
         <v>1</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +995,8 @@
       <c r="F22" t="n">
         <v>1</v>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -943,6 +1019,8 @@
       <c r="F23" t="n">
         <v>19</v>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1043,8 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1067,8 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1091,8 @@
       <c r="F26" t="n">
         <v>1</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1115,8 @@
       <c r="F27" t="n">
         <v>71</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1139,8 @@
       <c r="F28" t="n">
         <v>1</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1163,8 @@
       <c r="F29" t="n">
         <v>1</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1097,6 +1187,8 @@
       <c r="F30" t="n">
         <v>1</v>
       </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
